--- a/output/yearly_total_coral_cover_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_38_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256260497589385</v>
+        <v>1.249810415172483</v>
       </c>
       <c r="C3" t="n">
-        <v>4.581175345529153</v>
+        <v>4.677101913711108</v>
       </c>
       <c r="D3" t="n">
-        <v>6.081107362410584</v>
+        <v>6.140247844114413</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91854320552912</v>
+        <v>12.067160172998</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.390794742800913</v>
+        <v>1.364919827051926</v>
       </c>
       <c r="C4" t="n">
-        <v>4.992710197370401</v>
+        <v>5.268869960602522</v>
       </c>
       <c r="D4" t="n">
-        <v>6.314951416435901</v>
+        <v>6.483897379013126</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69845635660721</v>
+        <v>13.11768716666757</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.569260004084255</v>
+        <v>1.515488803236672</v>
       </c>
       <c r="C5" t="n">
-        <v>5.478239107486444</v>
+        <v>6.029030318137405</v>
       </c>
       <c r="D5" t="n">
-        <v>6.596098810045755</v>
+        <v>6.929781751915562</v>
       </c>
       <c r="E5" t="n">
-        <v>13.64359792161645</v>
+        <v>14.47430087328964</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.776251212761252</v>
+        <v>1.688300560036621</v>
       </c>
       <c r="C6" t="n">
-        <v>6.106171516211258</v>
+        <v>6.962895793728098</v>
       </c>
       <c r="D6" t="n">
-        <v>6.879206683345117</v>
+        <v>7.436220700385704</v>
       </c>
       <c r="E6" t="n">
-        <v>14.76162941231763</v>
+        <v>16.08741705415042</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.011270033432262</v>
+        <v>1.881415293623064</v>
       </c>
       <c r="C7" t="n">
-        <v>6.848970631124526</v>
+        <v>8.082270601392645</v>
       </c>
       <c r="D7" t="n">
-        <v>7.255353616005856</v>
+        <v>7.856355461153586</v>
       </c>
       <c r="E7" t="n">
-        <v>16.11559428056264</v>
+        <v>17.82004135616929</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.234781770755111</v>
+        <v>1.120177647849695</v>
       </c>
       <c r="C8" t="n">
-        <v>4.555495531533978</v>
+        <v>5.774372310871109</v>
       </c>
       <c r="D8" t="n">
-        <v>5.527874066459838</v>
+        <v>6.095522750273971</v>
       </c>
       <c r="E8" t="n">
-        <v>11.31815136874893</v>
+        <v>12.99007270899478</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.557886682193087</v>
+        <v>1.378631637761401</v>
       </c>
       <c r="C9" t="n">
-        <v>5.553836254006839</v>
+        <v>7.177228625636802</v>
       </c>
       <c r="D9" t="n">
-        <v>6.07441940773617</v>
+        <v>6.797991214540839</v>
       </c>
       <c r="E9" t="n">
-        <v>13.1861423439361</v>
+        <v>15.35385147793904</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.904394886552084</v>
+        <v>1.648622498307172</v>
       </c>
       <c r="C10" t="n">
-        <v>6.725754147146538</v>
+        <v>8.708153415966125</v>
       </c>
       <c r="D10" t="n">
-        <v>6.63808779211893</v>
+        <v>7.424348174210155</v>
       </c>
       <c r="E10" t="n">
-        <v>15.26823682581755</v>
+        <v>17.78112408848345</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.280895307043489</v>
+        <v>1.923795773362363</v>
       </c>
       <c r="C11" t="n">
-        <v>7.982621040270821</v>
+        <v>10.31033666585684</v>
       </c>
       <c r="D11" t="n">
-        <v>7.229946951604034</v>
+        <v>8.053612454184513</v>
       </c>
       <c r="E11" t="n">
-        <v>17.49346329891834</v>
+        <v>20.28774489340372</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.664168761776094</v>
+        <v>2.189342996960983</v>
       </c>
       <c r="C12" t="n">
-        <v>9.361776980403993</v>
+        <v>11.91534252293586</v>
       </c>
       <c r="D12" t="n">
-        <v>7.813676002928536</v>
+        <v>8.657632718360588</v>
       </c>
       <c r="E12" t="n">
-        <v>19.83962174510862</v>
+        <v>22.76231823825743</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.059302601031576</v>
+        <v>2.435726154409037</v>
       </c>
       <c r="C13" t="n">
-        <v>10.75182898708912</v>
+        <v>13.50004104118187</v>
       </c>
       <c r="D13" t="n">
-        <v>8.398289614286938</v>
+        <v>9.274700996960002</v>
       </c>
       <c r="E13" t="n">
-        <v>22.20942120240764</v>
+        <v>25.21046819255091</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.77371375978567</v>
+        <v>1.39741968222491</v>
       </c>
       <c r="C14" t="n">
-        <v>7.540224885174245</v>
+        <v>9.356301058398165</v>
       </c>
       <c r="D14" t="n">
-        <v>6.440903075866837</v>
+        <v>7.010954880337747</v>
       </c>
       <c r="E14" t="n">
-        <v>15.75484172082675</v>
+        <v>17.76467562096082</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.855532613457599</v>
+        <v>1.410673276232242</v>
       </c>
       <c r="C15" t="n">
-        <v>8.093920772892403</v>
+        <v>9.969520309424809</v>
       </c>
       <c r="D15" t="n">
-        <v>6.525510093018827</v>
+        <v>7.11542265354665</v>
       </c>
       <c r="E15" t="n">
-        <v>16.47496347936883</v>
+        <v>18.4956162392037</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.190014056294487</v>
+        <v>1.611911920648753</v>
       </c>
       <c r="C16" t="n">
-        <v>9.504495874354221</v>
+        <v>11.58669439776832</v>
       </c>
       <c r="D16" t="n">
-        <v>7.080452800321378</v>
+        <v>7.664661406687528</v>
       </c>
       <c r="E16" t="n">
-        <v>18.77496273097009</v>
+        <v>20.86326772510461</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.778435966243097</v>
+        <v>1.281681445371254</v>
       </c>
       <c r="C17" t="n">
-        <v>8.750052216071674</v>
+        <v>10.46456658929126</v>
       </c>
       <c r="D17" t="n">
-        <v>6.642279164961942</v>
+        <v>7.191822259891136</v>
       </c>
       <c r="E17" t="n">
-        <v>17.17076734727671</v>
+        <v>18.93807029455365</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.055710970353524</v>
+        <v>1.445957288722872</v>
       </c>
       <c r="C18" t="n">
-        <v>10.15868345707908</v>
+        <v>12.03488185971108</v>
       </c>
       <c r="D18" t="n">
-        <v>7.115442288500736</v>
+        <v>7.705580651000535</v>
       </c>
       <c r="E18" t="n">
-        <v>19.32983671593334</v>
+        <v>21.18641979943449</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.091260054724301</v>
+        <v>1.437033202091269</v>
       </c>
       <c r="C19" t="n">
-        <v>10.81756379383024</v>
+        <v>12.69428252274549</v>
       </c>
       <c r="D19" t="n">
-        <v>7.251070733842433</v>
+        <v>7.848032242886748</v>
       </c>
       <c r="E19" t="n">
-        <v>20.15989458239698</v>
+        <v>21.97934796772351</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.360730164585966</v>
+        <v>1.582734378878538</v>
       </c>
       <c r="C20" t="n">
-        <v>12.44138431413151</v>
+        <v>14.47860897521407</v>
       </c>
       <c r="D20" t="n">
-        <v>7.765074561877892</v>
+        <v>8.315815389006268</v>
       </c>
       <c r="E20" t="n">
-        <v>22.56718904059537</v>
+        <v>24.37715874309887</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.420814730017111</v>
+        <v>0.93266031903447</v>
       </c>
       <c r="C21" t="n">
-        <v>9.154002126461068</v>
+        <v>10.56731630401773</v>
       </c>
       <c r="D21" t="n">
-        <v>6.512875000065171</v>
+        <v>6.973344125788052</v>
       </c>
       <c r="E21" t="n">
-        <v>17.08769185654335</v>
+        <v>18.47332074884025</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_38_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249810415172483</v>
+        <v>1.261228140972873</v>
       </c>
       <c r="C3" t="n">
-        <v>4.677101913711108</v>
+        <v>4.633973737063545</v>
       </c>
       <c r="D3" t="n">
-        <v>6.140247844114413</v>
+        <v>6.060912812134227</v>
       </c>
       <c r="E3" t="n">
-        <v>12.067160172998</v>
+        <v>11.95611469017065</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.364919827051926</v>
+        <v>1.394106588417452</v>
       </c>
       <c r="C4" t="n">
-        <v>5.268869960602522</v>
+        <v>5.126999089764301</v>
       </c>
       <c r="D4" t="n">
-        <v>6.483897379013126</v>
+        <v>6.258745600176733</v>
       </c>
       <c r="E4" t="n">
-        <v>13.11768716666757</v>
+        <v>12.77985127835849</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.515488803236672</v>
+        <v>1.568422177419952</v>
       </c>
       <c r="C5" t="n">
-        <v>6.029030318137405</v>
+        <v>5.736163309263692</v>
       </c>
       <c r="D5" t="n">
-        <v>6.929781751915562</v>
+        <v>6.478637677642346</v>
       </c>
       <c r="E5" t="n">
-        <v>14.47430087328964</v>
+        <v>13.78322316432599</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.688300560036621</v>
+        <v>1.76054959049056</v>
       </c>
       <c r="C6" t="n">
-        <v>6.962895793728098</v>
+        <v>6.466967134687879</v>
       </c>
       <c r="D6" t="n">
-        <v>7.436220700385704</v>
+        <v>6.690685537493188</v>
       </c>
       <c r="E6" t="n">
-        <v>16.08741705415042</v>
+        <v>14.91820226267163</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.881415293623064</v>
+        <v>1.973747361072096</v>
       </c>
       <c r="C7" t="n">
-        <v>8.082270601392645</v>
+        <v>7.33771510099802</v>
       </c>
       <c r="D7" t="n">
-        <v>7.856355461153586</v>
+        <v>7.065479297712893</v>
       </c>
       <c r="E7" t="n">
-        <v>17.82004135616929</v>
+        <v>16.37694175978301</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.120177647849695</v>
+        <v>1.183489894074218</v>
       </c>
       <c r="C8" t="n">
-        <v>5.774372310871109</v>
+        <v>4.994221863926652</v>
       </c>
       <c r="D8" t="n">
-        <v>6.095522750273971</v>
+        <v>5.219819693732254</v>
       </c>
       <c r="E8" t="n">
-        <v>12.99007270899478</v>
+        <v>11.39753145173312</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.378631637761401</v>
+        <v>1.481266751723447</v>
       </c>
       <c r="C9" t="n">
-        <v>7.177228625636802</v>
+        <v>6.187373298217742</v>
       </c>
       <c r="D9" t="n">
-        <v>6.797991214540839</v>
+        <v>5.604961038973727</v>
       </c>
       <c r="E9" t="n">
-        <v>15.35385147793904</v>
+        <v>13.27360108891492</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.648622498307172</v>
+        <v>1.795584103442577</v>
       </c>
       <c r="C10" t="n">
-        <v>8.708153415966125</v>
+        <v>7.580004844193071</v>
       </c>
       <c r="D10" t="n">
-        <v>7.424348174210155</v>
+        <v>6.053865683227905</v>
       </c>
       <c r="E10" t="n">
-        <v>17.78112408848345</v>
+        <v>15.42945463086355</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.923795773362363</v>
+        <v>2.121882566398951</v>
       </c>
       <c r="C11" t="n">
-        <v>10.31033666585684</v>
+        <v>9.126727141284389</v>
       </c>
       <c r="D11" t="n">
-        <v>8.053612454184513</v>
+        <v>6.437980720769404</v>
       </c>
       <c r="E11" t="n">
-        <v>20.28774489340372</v>
+        <v>17.68659042845275</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.189342996960983</v>
+        <v>2.46810749200359</v>
       </c>
       <c r="C12" t="n">
-        <v>11.91534252293586</v>
+        <v>10.80185095755371</v>
       </c>
       <c r="D12" t="n">
-        <v>8.657632718360588</v>
+        <v>6.799841875902441</v>
       </c>
       <c r="E12" t="n">
-        <v>22.76231823825743</v>
+        <v>20.06980032545974</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.435726154409037</v>
+        <v>2.817354878985399</v>
       </c>
       <c r="C13" t="n">
-        <v>13.50004104118187</v>
+        <v>12.58577424049643</v>
       </c>
       <c r="D13" t="n">
-        <v>9.274700996960002</v>
+        <v>7.200701586509046</v>
       </c>
       <c r="E13" t="n">
-        <v>25.21046819255091</v>
+        <v>22.60383070599087</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.39741968222491</v>
+        <v>1.642493361636041</v>
       </c>
       <c r="C14" t="n">
-        <v>9.356301058398165</v>
+        <v>8.846400935766455</v>
       </c>
       <c r="D14" t="n">
-        <v>7.010954880337747</v>
+        <v>5.50491463211497</v>
       </c>
       <c r="E14" t="n">
-        <v>17.76467562096082</v>
+        <v>15.99380892951747</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.410673276232242</v>
+        <v>1.699042029400657</v>
       </c>
       <c r="C15" t="n">
-        <v>9.969520309424809</v>
+        <v>9.738662336771171</v>
       </c>
       <c r="D15" t="n">
-        <v>7.11542265354665</v>
+        <v>5.435318537360913</v>
       </c>
       <c r="E15" t="n">
-        <v>18.4956162392037</v>
+        <v>16.87302290353274</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.611911920648753</v>
+        <v>1.994067032003866</v>
       </c>
       <c r="C16" t="n">
-        <v>11.58669439776832</v>
+        <v>11.68080473269742</v>
       </c>
       <c r="D16" t="n">
-        <v>7.664661406687528</v>
+        <v>5.812908521891279</v>
       </c>
       <c r="E16" t="n">
-        <v>20.86326772510461</v>
+        <v>19.48778028659257</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.281681445371254</v>
+        <v>1.613904868488374</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46456658929126</v>
+        <v>10.92694030556038</v>
       </c>
       <c r="D17" t="n">
-        <v>7.191822259891136</v>
+        <v>5.316124548588308</v>
       </c>
       <c r="E17" t="n">
-        <v>18.93807029455365</v>
+        <v>17.85696972263706</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.445957288722872</v>
+        <v>1.854059991901229</v>
       </c>
       <c r="C18" t="n">
-        <v>12.03488185971108</v>
+        <v>12.84353762622213</v>
       </c>
       <c r="D18" t="n">
-        <v>7.705580651000535</v>
+        <v>5.65487659393867</v>
       </c>
       <c r="E18" t="n">
-        <v>21.18641979943449</v>
+        <v>20.35247421206203</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.437033202091269</v>
+        <v>1.868285516135765</v>
       </c>
       <c r="C19" t="n">
-        <v>12.69428252274549</v>
+        <v>13.81600781466381</v>
       </c>
       <c r="D19" t="n">
-        <v>7.848032242886748</v>
+        <v>5.694666828391794</v>
       </c>
       <c r="E19" t="n">
-        <v>21.97934796772351</v>
+        <v>21.37896015919137</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.582734378878538</v>
+        <v>2.084054026575129</v>
       </c>
       <c r="C20" t="n">
-        <v>14.47860897521407</v>
+        <v>15.87628391184209</v>
       </c>
       <c r="D20" t="n">
-        <v>8.315815389006268</v>
+        <v>6.018751563040708</v>
       </c>
       <c r="E20" t="n">
-        <v>24.37715874309887</v>
+        <v>23.97908950145792</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.93266031903447</v>
+        <v>1.241429789497134</v>
       </c>
       <c r="C21" t="n">
-        <v>10.56731630401773</v>
+        <v>11.60246126589853</v>
       </c>
       <c r="D21" t="n">
-        <v>6.973344125788052</v>
+        <v>4.98255613111637</v>
       </c>
       <c r="E21" t="n">
-        <v>18.47332074884025</v>
+        <v>17.82644718651203</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_38_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_38_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261228140972873</v>
+        <v>2.612744322149651</v>
       </c>
       <c r="C3" t="n">
-        <v>4.633973737063545</v>
+        <v>7.739840815235254</v>
       </c>
       <c r="D3" t="n">
-        <v>6.060912812134227</v>
+        <v>8.114878891435493</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95611469017065</v>
+        <v>18.4674640288204</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.394106588417452</v>
+        <v>1.127491608493823</v>
       </c>
       <c r="C4" t="n">
-        <v>5.126999089764301</v>
+        <v>4.579860971599072</v>
       </c>
       <c r="D4" t="n">
-        <v>6.258745600176733</v>
+        <v>5.767208396762029</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77985127835849</v>
+        <v>11.47456097685492</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.568422177419952</v>
+        <v>1.27549390517239</v>
       </c>
       <c r="C5" t="n">
-        <v>5.736163309263692</v>
+        <v>5.312750394010422</v>
       </c>
       <c r="D5" t="n">
-        <v>6.478637677642346</v>
+        <v>6.026723634290534</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78322316432599</v>
+        <v>12.61496793347335</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.76054959049056</v>
+        <v>1.438891948121028</v>
       </c>
       <c r="C6" t="n">
-        <v>6.466967134687879</v>
+        <v>6.228384703098877</v>
       </c>
       <c r="D6" t="n">
-        <v>6.690685537493188</v>
+        <v>6.395962478936887</v>
       </c>
       <c r="E6" t="n">
-        <v>14.91820226267163</v>
+        <v>14.06323913015679</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.973747361072096</v>
+        <v>1.607420685508174</v>
       </c>
       <c r="C7" t="n">
-        <v>7.33771510099802</v>
+        <v>7.309179687483589</v>
       </c>
       <c r="D7" t="n">
-        <v>7.065479297712893</v>
+        <v>6.795031411967471</v>
       </c>
       <c r="E7" t="n">
-        <v>16.37694175978301</v>
+        <v>15.71163178495923</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.183489894074218</v>
+        <v>1.781064886639904</v>
       </c>
       <c r="C8" t="n">
-        <v>4.994221863926652</v>
+        <v>8.573443123753373</v>
       </c>
       <c r="D8" t="n">
-        <v>5.219819693732254</v>
+        <v>7.269536867296671</v>
       </c>
       <c r="E8" t="n">
-        <v>11.39753145173312</v>
+        <v>17.62404487768995</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.481266751723447</v>
+        <v>1.936689674527681</v>
       </c>
       <c r="C9" t="n">
-        <v>6.187373298217742</v>
+        <v>10.03192461712067</v>
       </c>
       <c r="D9" t="n">
-        <v>5.604961038973727</v>
+        <v>7.744506722729626</v>
       </c>
       <c r="E9" t="n">
-        <v>13.27360108891492</v>
+        <v>19.71312101437797</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.795584103442577</v>
+        <v>1.179530596744373</v>
       </c>
       <c r="C10" t="n">
-        <v>7.580004844193071</v>
+        <v>7.394533525864019</v>
       </c>
       <c r="D10" t="n">
-        <v>6.053865683227905</v>
+        <v>6.118624756993736</v>
       </c>
       <c r="E10" t="n">
-        <v>15.42945463086355</v>
+        <v>14.69268887960213</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.121882566398951</v>
+        <v>1.121185330680985</v>
       </c>
       <c r="C11" t="n">
-        <v>9.126727141284389</v>
+        <v>8.053934188898431</v>
       </c>
       <c r="D11" t="n">
-        <v>6.437980720769404</v>
+        <v>6.013037791401991</v>
       </c>
       <c r="E11" t="n">
-        <v>17.68659042845275</v>
+        <v>15.18815731098141</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.46810749200359</v>
+        <v>1.218623790327481</v>
       </c>
       <c r="C12" t="n">
-        <v>10.80185095755371</v>
+        <v>9.677528907227721</v>
       </c>
       <c r="D12" t="n">
-        <v>6.799841875902441</v>
+        <v>6.44286657127533</v>
       </c>
       <c r="E12" t="n">
-        <v>20.06980032545974</v>
+        <v>17.33901926883053</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.817354878985399</v>
+        <v>0.9603848742023998</v>
       </c>
       <c r="C13" t="n">
-        <v>12.58577424049643</v>
+        <v>9.322185325675589</v>
       </c>
       <c r="D13" t="n">
-        <v>7.200701586509046</v>
+        <v>5.916777429000592</v>
       </c>
       <c r="E13" t="n">
-        <v>22.60383070599087</v>
+        <v>16.19934762887858</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.642493361636041</v>
+        <v>1.037687688434794</v>
       </c>
       <c r="C14" t="n">
-        <v>8.846400935766455</v>
+        <v>11.02744181804413</v>
       </c>
       <c r="D14" t="n">
-        <v>5.50491463211497</v>
+        <v>6.298431849026539</v>
       </c>
       <c r="E14" t="n">
-        <v>15.99380892951747</v>
+        <v>18.36356135550546</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.699042029400657</v>
+        <v>1.002452763329376</v>
       </c>
       <c r="C15" t="n">
-        <v>9.738662336771171</v>
+        <v>11.99474801356147</v>
       </c>
       <c r="D15" t="n">
-        <v>5.435318537360913</v>
+        <v>6.357552695776283</v>
       </c>
       <c r="E15" t="n">
-        <v>16.87302290353274</v>
+        <v>19.35475347266713</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.994067032003866</v>
+        <v>1.088237877726462</v>
       </c>
       <c r="C16" t="n">
-        <v>11.68080473269742</v>
+        <v>13.98414192649312</v>
       </c>
       <c r="D16" t="n">
-        <v>5.812908521891279</v>
+        <v>6.788284683537528</v>
       </c>
       <c r="E16" t="n">
-        <v>19.48778028659257</v>
+        <v>21.86066448775711</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.613904868488374</v>
+        <v>0.6445860901773284</v>
       </c>
       <c r="C17" t="n">
-        <v>10.92694030556038</v>
+        <v>10.43264015394915</v>
       </c>
       <c r="D17" t="n">
-        <v>5.316124548588308</v>
+        <v>5.663604331029425</v>
       </c>
       <c r="E17" t="n">
-        <v>17.85696972263706</v>
+        <v>16.74083057515591</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.854059991901229</v>
+        <v>0.5098706702005811</v>
       </c>
       <c r="C18" t="n">
-        <v>12.84353762622213</v>
+        <v>9.40580077764629</v>
       </c>
       <c r="D18" t="n">
-        <v>5.65487659393867</v>
+        <v>5.195153596471017</v>
       </c>
       <c r="E18" t="n">
-        <v>20.35247421206203</v>
+        <v>15.11082504431789</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.868285516135765</v>
+        <v>0.5919742307067418</v>
       </c>
       <c r="C19" t="n">
-        <v>13.81600781466381</v>
+        <v>11.58410258382911</v>
       </c>
       <c r="D19" t="n">
-        <v>5.694666828391794</v>
+        <v>5.687598244921216</v>
       </c>
       <c r="E19" t="n">
-        <v>21.37896015919137</v>
+        <v>17.86367505945707</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.084054026575129</v>
+        <v>0.6709951034215674</v>
       </c>
       <c r="C20" t="n">
-        <v>15.87628391184209</v>
+        <v>13.80013295428614</v>
       </c>
       <c r="D20" t="n">
-        <v>6.018751563040708</v>
+        <v>6.233135809217084</v>
       </c>
       <c r="E20" t="n">
-        <v>23.97908950145792</v>
+        <v>20.70426386692479</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.241429789497134</v>
+        <v>0.7440764025257001</v>
       </c>
       <c r="C21" t="n">
-        <v>11.60246126589853</v>
+        <v>15.98876274631764</v>
       </c>
       <c r="D21" t="n">
-        <v>4.98255613111637</v>
+        <v>6.680557507950525</v>
       </c>
       <c r="E21" t="n">
-        <v>17.82644718651203</v>
+        <v>23.41339665679386</v>
       </c>
     </row>
   </sheetData>
